--- a/research/traditional_assets/database/data/india/india_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/india/india_homebuilding.xlsx
@@ -587,23 +587,29 @@
           <t>Homebuilding</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.67</v>
+      </c>
+      <c r="E2">
+        <v>0.0517</v>
+      </c>
       <c r="G2">
-        <v>0.09925925925925926</v>
+        <v>0.02754491017964072</v>
       </c>
       <c r="H2">
-        <v>0.09925925925925926</v>
+        <v>0.02754491017964072</v>
       </c>
       <c r="I2">
-        <v>0.07407407407407407</v>
+        <v>0.02634730538922156</v>
       </c>
       <c r="J2">
-        <v>0.04938271604938271</v>
+        <v>0.02634730538922156</v>
       </c>
       <c r="K2">
-        <v>0.068</v>
+        <v>0.025</v>
       </c>
       <c r="L2">
-        <v>0.05037037037037037</v>
+        <v>0.02994011976047905</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,70 +633,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.06900000000000001</v>
+        <v>0.007</v>
       </c>
       <c r="V2">
-        <v>0.007700892857142857</v>
+        <v>0.001301115241635688</v>
       </c>
       <c r="W2">
-        <v>0.02281879194630873</v>
+        <v>0.008445945945945946</v>
       </c>
       <c r="X2">
-        <v>0.1358815017784082</v>
+        <v>0.1143758696637047</v>
       </c>
       <c r="Y2">
-        <v>-0.1130627098320995</v>
+        <v>-0.1059299237177587</v>
       </c>
       <c r="Z2">
-        <v>0.3918722786647316</v>
+        <v>0.2555861646770737</v>
       </c>
       <c r="AA2">
-        <v>0.01935171746492501</v>
+        <v>0.006734006734006733</v>
       </c>
       <c r="AB2">
-        <v>0.1337012592768599</v>
+        <v>0.1142197568888911</v>
       </c>
       <c r="AC2">
-        <v>-0.1143495418119349</v>
+        <v>-0.1074857501548844</v>
       </c>
       <c r="AD2">
-        <v>0.265</v>
+        <v>0.014</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.265</v>
+        <v>0.014</v>
       </c>
       <c r="AG2">
-        <v>0.196</v>
+        <v>0.007</v>
       </c>
       <c r="AH2">
-        <v>0.02872628726287263</v>
+        <v>0.002595476455320727</v>
       </c>
       <c r="AI2">
-        <v>0.08674304418985269</v>
+        <v>0.005046863734679164</v>
       </c>
       <c r="AJ2">
-        <v>0.02140672782874618</v>
+        <v>0.001299424540560609</v>
       </c>
       <c r="AK2">
-        <v>0.06563965170797052</v>
+        <v>0.002529815684857246</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AN2">
-        <v>2.65</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="AP2">
-        <v>1.96</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="AQ2">
-        <v>-100</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="3">
@@ -709,23 +715,29 @@
           <t>Homebuilding</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.67</v>
+      </c>
+      <c r="E3">
+        <v>0.0517</v>
+      </c>
       <c r="G3">
-        <v>0.09925925925925926</v>
+        <v>0.02754491017964072</v>
       </c>
       <c r="H3">
-        <v>0.09925925925925926</v>
+        <v>0.02754491017964072</v>
       </c>
       <c r="I3">
-        <v>0.07407407407407407</v>
+        <v>0.02634730538922156</v>
       </c>
       <c r="J3">
-        <v>0.04938271604938271</v>
+        <v>0.02634730538922156</v>
       </c>
       <c r="K3">
-        <v>0.068</v>
+        <v>0.025</v>
       </c>
       <c r="L3">
-        <v>0.05037037037037037</v>
+        <v>0.02994011976047905</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,70 +761,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.06900000000000001</v>
+        <v>0.007</v>
       </c>
       <c r="V3">
-        <v>0.007700892857142857</v>
+        <v>0.001301115241635688</v>
       </c>
       <c r="W3">
-        <v>0.02281879194630873</v>
+        <v>0.008445945945945946</v>
       </c>
       <c r="X3">
-        <v>0.1358815017784082</v>
+        <v>0.1143758696637047</v>
       </c>
       <c r="Y3">
-        <v>-0.1130627098320995</v>
+        <v>-0.1059299237177587</v>
       </c>
       <c r="Z3">
-        <v>0.3918722786647316</v>
+        <v>0.2555861646770737</v>
       </c>
       <c r="AA3">
-        <v>0.01935171746492501</v>
+        <v>0.006734006734006733</v>
       </c>
       <c r="AB3">
-        <v>0.1337012592768599</v>
+        <v>0.1142197568888911</v>
       </c>
       <c r="AC3">
-        <v>-0.1143495418119349</v>
+        <v>-0.1074857501548844</v>
       </c>
       <c r="AD3">
-        <v>0.265</v>
+        <v>0.014</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.265</v>
+        <v>0.014</v>
       </c>
       <c r="AG3">
-        <v>0.196</v>
+        <v>0.007</v>
       </c>
       <c r="AH3">
-        <v>0.02872628726287263</v>
+        <v>0.002595476455320727</v>
       </c>
       <c r="AI3">
-        <v>0.08674304418985269</v>
+        <v>0.005046863734679164</v>
       </c>
       <c r="AJ3">
-        <v>0.02140672782874618</v>
+        <v>0.001299424540560609</v>
       </c>
       <c r="AK3">
-        <v>0.06563965170797052</v>
+        <v>0.002529815684857246</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AN3">
-        <v>2.65</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="AP3">
-        <v>1.96</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="AQ3">
-        <v>-100</v>
+        <v>-11</v>
       </c>
     </row>
   </sheetData>
